--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:21:15+00:00</t>
+    <t>2026-03-09T10:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:11:56+00:00</t>
+    <t>2026-03-09T10:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:54:50+00:00</t>
+    <t>2026-03-09T16:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1077,6 +1077,37 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>Goal.target.measure.id</t>
+  </si>
+  <si>
+    <t>Goal.target.measure.extension</t>
+  </si>
+  <si>
+    <t>Goal.target.measure.extension:DataAbsentReason</t>
+  </si>
+  <si>
+    <t>DataAbsentReason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {data-absent-reason}
+</t>
+  </si>
+  <si>
+    <t>unknown | asked | temp | notasked | masked | unsupported | astext | error</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value or elements in the element that is extended are missing.</t>
+  </si>
+  <si>
+    <t>ANY.nullFlavor</t>
+  </si>
+  <si>
+    <t>Goal.target.measure.coding</t>
+  </si>
+  <si>
+    <t>Goal.target.measure.text</t>
   </si>
   <si>
     <t>Goal.target.detail[x]</t>
@@ -1561,11 +1592,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN51"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.62890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.9140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -6200,20 +6231,18 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>344</v>
+        <v>156</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>157</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6238,10 +6267,10 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>348</v>
+        <v>77</v>
       </c>
       <c r="Z41" t="s" s="2">
         <v>77</v>
@@ -6250,17 +6279,19 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>159</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6269,10 +6300,10 @@
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6281,7 +6312,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6289,23 +6320,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6314,20 +6343,18 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>345</v>
+        <v>236</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6352,10 +6379,10 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>348</v>
+        <v>77</v>
       </c>
       <c r="Z42" t="s" s="2">
         <v>77</v>
@@ -6364,34 +6391,34 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>343</v>
+        <v>166</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
@@ -6405,18 +6432,20 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6428,21 +6457,19 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>356</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6478,29 +6505,31 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>166</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6509,22 +6538,20 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>357</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6533,7 +6560,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6545,17 +6572,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>321</v>
+        <v>284</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>354</v>
+        <v>285</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6604,13 +6633,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>289</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6619,24 +6648,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>357</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6659,18 +6688,20 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>321</v>
+        <v>156</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>362</v>
+        <v>293</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
+        <v>294</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6718,7 +6749,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6736,21 +6767,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>300</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6770,19 +6801,19 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>156</v>
+        <v>354</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6808,10 +6839,10 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>77</v>
@@ -6820,19 +6851,17 @@
         <v>77</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6841,7 +6870,7 @@
         <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
@@ -6861,12 +6890,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
       </c>
@@ -6887,16 +6918,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>371</v>
+        <v>156</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6922,10 +6953,10 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>77</v>
@@ -6946,7 +6977,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6955,13 +6986,13 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -6970,15 +7001,15 @@
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6989,7 +7020,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -6998,20 +7029,20 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7048,25 +7079,23 @@
         <v>77</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
@@ -7081,20 +7110,22 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7103,7 +7134,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7112,22 +7143,20 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7176,13 +7205,13 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7191,24 +7220,24 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>77</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7219,7 +7248,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7228,23 +7257,21 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>178</v>
+        <v>321</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7268,13 +7295,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7292,13 +7319,13 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7316,15 +7343,15 @@
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7335,7 +7362,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7347,20 +7374,18 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>398</v>
+        <v>156</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7408,13 +7433,13 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
@@ -7432,6 +7457,582 @@
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T16:16:18+00:00</t>
+    <t>2026-03-16T17:28:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,13 +326,193 @@
 </t>
   </si>
   <si>
-    <t>Goal.implicitRules</t>
+    <t>Goal.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Goal.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Goal.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Goal.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Statut.dateStatut</t>
+  </si>
+  <si>
+    <t>Goal.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Goal.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Goal.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Goal.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Goal.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -428,28 +608,10 @@
     <t>Goal.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Goal.modifierExtension</t>
@@ -475,7 +637,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'attente</t>
+    <t>Identifiant du projet de vie</t>
   </si>
   <si>
     <t>Business identifiers assigned to this goal by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -499,39 +661,7 @@
     <t>Goal.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Goal.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Goal.identifier.use</t>
@@ -583,9 +713,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -702,7 +829,7 @@
     <t>Goal.lifecycleStatus</t>
   </si>
   <si>
-    <t>proposed | planned | accepted | active | on-hold | completed | cancelled | entered-in-error | rejected</t>
+    <t>Correspondance des statuts métier avec les codes FHIR : ENPREPARATION → planned, ENCOURS → active, TERMINE → completed.</t>
   </si>
   <si>
     <t>The state of the goal throughout its lifecycle.</t>
@@ -810,9 +937,6 @@
   </si>
   <si>
     <t>Allows goals to be filtered and sorted.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes for grouping and sorting goals.</t>
@@ -892,10 +1016,6 @@
     <t>Goal.description.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Code defined by a terminology system</t>
   </si>
   <si>
@@ -1135,7 +1255,7 @@
     <t>detailString</t>
   </si>
   <si>
-    <t>aspirationProjetVie</t>
+    <t>aspirationSouhait</t>
   </si>
   <si>
     <t>Goal.target.due[x]</t>
@@ -1592,7 +1712,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN56"/>
+  <dimension ref="A1:AN64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.9140625" customWidth="true" bestFit="true"/>
@@ -2120,10 +2240,10 @@
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>103</v>
@@ -2134,9 +2254,7 @@
       <c r="M5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>77</v>
@@ -2185,7 +2303,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2197,7 +2315,7 @@
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2206,7 +2324,7 @@
         <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>77</v>
@@ -2221,14 +2339,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2240,16 +2358,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2275,43 +2393,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2320,7 +2438,7 @@
         <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>77</v>
@@ -2328,14 +2446,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2351,10 +2469,10 @@
         <v>77</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>120</v>
@@ -2434,7 +2552,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2442,21 +2560,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>77</v>
@@ -2465,19 +2583,19 @@
         <v>77</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2527,28 +2645,28 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2556,21 +2674,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>77</v>
@@ -2579,19 +2697,19 @@
         <v>77</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2641,19 +2759,19 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2662,7 +2780,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2670,14 +2788,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2690,26 +2808,24 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>77</v>
       </c>
@@ -2757,7 +2873,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2769,7 +2885,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2778,7 +2894,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2786,10 +2902,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2797,10 +2913,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>77</v>
@@ -2809,23 +2925,21 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>77</v>
       </c>
@@ -2849,13 +2963,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2873,7 +2987,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2888,24 +3002,24 @@
         <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2916,7 +3030,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2925,18 +3039,20 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2961,13 +3077,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2991,13 +3107,13 @@
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
@@ -3006,7 +3122,7 @@
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3014,42 +3130,42 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3087,31 +3203,31 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
@@ -3120,7 +3236,7 @@
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3128,10 +3244,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3148,26 +3264,24 @@
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3191,31 +3305,31 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3233,10 +3347,10 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -3244,14 +3358,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3267,23 +3381,21 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>182</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3307,13 +3419,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3331,7 +3443,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3349,10 +3461,10 @@
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -3360,21 +3472,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3383,23 +3495,21 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3408,10 +3518,10 @@
         <v>77</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>77</v>
@@ -3447,28 +3557,28 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3476,21 +3586,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3499,19 +3609,19 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3525,7 +3635,7 @@
         <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>77</v>
@@ -3561,28 +3671,28 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3590,42 +3700,46 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>207</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3673,28 +3787,28 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3702,10 +3816,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3713,7 +3827,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3725,21 +3839,23 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3787,13 +3903,13 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
@@ -3802,24 +3918,24 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3827,7 +3943,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3836,26 +3952,22 @@
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3879,13 +3991,13 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3903,10 +4015,10 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -3915,38 +4027,38 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>107</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -3958,15 +4070,17 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>111</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4003,31 +4117,31 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -4036,7 +4150,7 @@
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4044,10 +4158,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4058,28 +4172,32 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4103,50 +4221,52 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4154,14 +4274,12 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4179,19 +4297,23 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4215,13 +4337,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4239,28 +4361,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4268,10 +4390,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4279,7 +4401,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
@@ -4291,19 +4413,23 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4312,10 +4438,10 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>77</v>
@@ -4351,7 +4477,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4363,16 +4489,16 @@
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4380,10 +4506,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4391,7 +4517,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>89</v>
@@ -4406,15 +4532,17 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4427,7 +4555,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4439,13 +4567,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4463,7 +4591,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4481,10 +4609,10 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4492,10 +4620,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4506,7 +4634,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4518,18 +4646,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>178</v>
+        <v>248</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4553,13 +4679,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>77</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4577,13 +4703,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4595,21 +4721,21 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4632,20 +4758,18 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4669,13 +4793,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4693,7 +4817,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4711,21 +4835,21 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4742,25 +4866,25 @@
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4785,13 +4909,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4809,7 +4933,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>89</v>
@@ -4824,24 +4948,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4864,13 +4988,13 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>157</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>158</v>
+        <v>275</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4921,7 +5045,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4942,7 +5066,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4950,14 +5074,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4976,17 +5100,15 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5023,19 +5145,17 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5047,7 +5167,7 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -5056,7 +5176,7 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5064,12 +5184,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5078,7 +5200,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5087,23 +5209,19 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5151,7 +5269,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>289</v>
+        <v>117</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5160,19 +5278,19 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5180,10 +5298,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5191,7 +5309,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5203,23 +5321,19 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5267,7 +5381,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5279,16 +5393,16 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5296,10 +5410,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5307,7 +5421,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -5322,18 +5436,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>302</v>
+        <v>220</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>305</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5357,13 +5469,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5381,10 +5493,10 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -5396,24 +5508,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5424,7 +5536,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5436,17 +5548,17 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>311</v>
+        <v>220</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5471,35 +5583,37 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -5517,19 +5631,17 @@
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5550,17 +5662,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>321</v>
+        <v>220</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5585,13 +5699,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>307</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5609,7 +5723,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5624,24 +5738,24 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>322</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5649,10 +5763,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5661,22 +5775,22 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>220</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5701,13 +5815,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>77</v>
+        <v>316</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5725,39 +5839,39 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>330</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>77</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5780,13 +5894,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5837,7 +5951,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5858,7 +5972,7 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5866,14 +5980,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5892,16 +6006,16 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5939,19 +6053,19 @@
         <v>77</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5963,7 +6077,7 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -5972,7 +6086,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5980,14 +6094,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>334</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6000,25 +6114,25 @@
         <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>138</v>
+        <v>326</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>144</v>
+        <v>327</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6067,7 +6181,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6079,16 +6193,16 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6096,10 +6210,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6107,7 +6221,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6122,16 +6236,20 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6155,13 +6273,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6179,7 +6297,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6188,19 +6306,19 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>77</v>
+        <v>337</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6208,10 +6326,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6219,7 +6337,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -6231,19 +6349,21 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>156</v>
+        <v>341</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>157</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>158</v>
+        <v>343</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6291,10 +6411,10 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>159</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -6303,27 +6423,27 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>77</v>
+        <v>346</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>160</v>
+        <v>347</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6331,11 +6451,11 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6343,19 +6463,21 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>350</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>236</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>237</v>
+        <v>352</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6379,43 +6501,41 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>77</v>
+        <v>355</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>166</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6427,25 +6547,25 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6457,19 +6577,21 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6517,39 +6639,39 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>166</v>
+        <v>349</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6569,22 +6691,22 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>284</v>
+        <v>363</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>285</v>
+        <v>364</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>287</v>
+        <v>366</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>288</v>
+        <v>367</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6633,7 +6755,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>289</v>
+        <v>362</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6642,19 +6764,19 @@
         <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>369</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6662,10 +6784,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6685,23 +6807,19 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>293</v>
+        <v>104</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6749,7 +6867,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>106</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6761,16 +6879,16 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>300</v>
+        <v>107</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6778,21 +6896,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6801,19 +6919,19 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>110</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>355</v>
+        <v>111</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
+        <v>112</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>357</v>
+        <v>113</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6839,10 +6957,10 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>77</v>
@@ -6851,29 +6969,31 @@
         <v>77</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>117</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6882,7 +7002,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6890,46 +7010,46 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -6953,10 +7073,10 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>77</v>
@@ -6977,28 +7097,28 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7006,10 +7126,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7032,18 +7152,16 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>363</v>
+        <v>220</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>366</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7067,29 +7185,31 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7098,7 +7218,7 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
@@ -7113,19 +7233,17 @@
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7143,21 +7261,19 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>321</v>
+        <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>104</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
+        <v>105</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>366</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7205,7 +7321,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>106</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7217,27 +7333,27 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7245,10 +7361,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7257,20 +7373,18 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>321</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>372</v>
+        <v>277</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7307,31 +7421,31 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>371</v>
+        <v>117</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7343,23 +7457,25 @@
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -7374,17 +7490,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>156</v>
+        <v>386</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7433,19 +7547,19 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>376</v>
+        <v>117</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
@@ -7454,7 +7568,7 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7462,10 +7576,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7476,7 +7590,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7488,18 +7602,20 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>381</v>
+        <v>144</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7547,13 +7663,13 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>380</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
@@ -7565,21 +7681,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7590,7 +7706,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7599,20 +7715,22 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>103</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>390</v>
+        <v>335</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7661,13 +7779,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>336</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -7679,21 +7797,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>391</v>
+        <v>339</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7704,7 +7822,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7713,23 +7831,21 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N54" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7753,10 +7869,10 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>397</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>77</v>
@@ -7765,28 +7881,26 @@
         <v>77</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
@@ -7795,10 +7909,10 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7806,12 +7920,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
       </c>
@@ -7820,7 +7936,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7829,23 +7945,21 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -7869,13 +7983,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7893,22 +8007,22 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>77</v>
+        <v>400</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7922,10 +8036,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7936,7 +8050,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -7945,20 +8059,18 @@
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
         <v>405</v>
       </c>
@@ -7997,25 +8109,23 @@
         <v>77</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -8033,6 +8143,926 @@
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T17:28:45+00:00</t>
+    <t>2026-06-10T07:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -649,6 +649,10 @@
     <t>Allows identification of the goal as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:type}
+</t>
+  </si>
+  <si>
     <t>idProjetVie</t>
   </si>
   <si>
@@ -658,12 +662,30 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>Goal.identifier:idPDV</t>
+  </si>
+  <si>
+    <t>idPDV</t>
+  </si>
+  <si>
+    <t>External Ids for this goal</t>
+  </si>
+  <si>
+    <t>Goal.identifier:idPDV.id</t>
+  </si>
+  <si>
     <t>Goal.identifier.id</t>
   </si>
   <si>
+    <t>Goal.identifier:idPDV.extension</t>
+  </si>
+  <si>
     <t>Goal.identifier.extension</t>
   </si>
   <si>
+    <t>Goal.identifier:idPDV.use</t>
+  </si>
+  <si>
     <t>Goal.identifier.use</t>
   </si>
   <si>
@@ -692,6 +714,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Goal.identifier:idPDV.type</t>
   </si>
   <si>
     <t>Goal.identifier.type</t>
@@ -713,6 +738,14 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-goal-identifier"/&gt;
+    &lt;code value="PDV"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -725,6 +758,9 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>Goal.identifier:idPDV.system</t>
+  </si>
+  <si>
     <t>Goal.identifier.system</t>
   </si>
   <si>
@@ -755,6 +791,9 @@
     <t>II.root or Role.id.root</t>
   </si>
   <si>
+    <t>Goal.identifier:idPDV.value</t>
+  </si>
+  <si>
     <t>Goal.identifier.value</t>
   </si>
   <si>
@@ -777,6 +816,9 @@
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Goal.identifier:idPDV.period</t>
   </si>
   <si>
     <t>Goal.identifier.period</t>
@@ -799,6 +841,9 @@
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Goal.identifier:idPDV.assigner</t>
   </si>
   <si>
     <t>Goal.identifier.assigner</t>
@@ -1712,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN64"/>
+  <dimension ref="A1:AN65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.9140625" customWidth="true" bestFit="true"/>
@@ -3830,7 +3875,7 @@
         <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3891,16 +3936,14 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>198</v>
@@ -3918,32 +3961,34 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3958,16 +4003,20 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4015,19 +4064,19 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -4036,29 +4085,29 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>107</v>
+        <v>206</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4070,17 +4119,15 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4117,31 +4164,31 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -4158,46 +4205,44 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>112</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4221,52 +4266,52 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>215</v>
+        <v>77</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>117</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>218</v>
+        <v>107</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4274,10 +4319,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4294,25 +4339,25 @@
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4337,13 +4382,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>148</v>
+        <v>221</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4361,7 +4406,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4379,10 +4424,10 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4390,10 +4435,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4416,19 +4461,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4438,28 +4483,28 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="T24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4498,7 +4543,7 @@
         <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4506,7 +4551,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>239</v>
@@ -4532,7 +4577,7 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>240</v>
@@ -4543,7 +4588,9 @@
       <c r="N25" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4552,10 +4599,10 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4591,7 +4638,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4609,10 +4656,10 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4620,10 +4667,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4631,7 +4678,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>89</v>
@@ -4646,15 +4693,17 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>248</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4667,7 +4716,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4703,7 +4752,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4721,10 +4770,10 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4732,10 +4781,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4758,17 +4807,15 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4817,7 +4864,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4835,10 +4882,10 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4846,10 +4893,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4857,7 +4904,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>89</v>
@@ -4866,26 +4913,24 @@
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4909,13 +4954,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4933,10 +4978,10 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>89</v>
@@ -4948,24 +4993,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4973,7 +5018,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -4982,22 +5027,26 @@
         <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -5021,13 +5070,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5045,10 +5094,10 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>106</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5057,27 +5106,27 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5088,7 +5137,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5100,13 +5149,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5145,29 +5194,31 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -5184,14 +5235,12 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5200,7 +5249,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5212,13 +5261,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>281</v>
+        <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5257,16 +5306,14 @@
         <v>77</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>117</v>
@@ -5278,13 +5325,13 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>118</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -5298,12 +5345,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5324,13 +5373,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>103</v>
+        <v>294</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5381,22 +5430,22 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>117</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>297</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
@@ -5410,10 +5459,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5433,16 +5482,16 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5469,13 +5518,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5493,7 +5542,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5505,7 +5554,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5514,7 +5563,7 @@
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5522,10 +5571,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5536,7 +5585,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5548,18 +5597,16 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>298</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5583,13 +5630,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5607,13 +5654,13 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -5628,18 +5675,18 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5650,7 +5697,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5662,19 +5709,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5699,37 +5744,37 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Z35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -5744,18 +5789,18 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5763,7 +5808,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
@@ -5778,19 +5823,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5815,13 +5860,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5839,10 +5884,10 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -5857,21 +5902,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5879,7 +5924,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -5891,19 +5936,23 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>103</v>
+        <v>228</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>104</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5927,13 +5976,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5951,10 +6000,10 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>106</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -5963,38 +6012,38 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>107</v>
+        <v>332</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>77</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -6006,17 +6055,15 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6053,31 +6100,31 @@
         <v>77</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -6094,14 +6141,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6117,23 +6164,21 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>111</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
+        <v>112</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6169,19 +6214,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>117</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6193,16 +6238,16 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>330</v>
+        <v>107</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6210,10 +6255,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6221,10 +6266,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6236,19 +6281,19 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6297,13 +6342,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6312,13 +6357,13 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>337</v>
+        <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6326,10 +6371,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6352,17 +6397,19 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>341</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6411,10 +6458,10 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -6426,24 +6473,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>348</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6451,7 +6498,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -6466,17 +6513,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6501,32 +6548,34 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -6538,28 +6587,26 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6580,17 +6627,17 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6615,31 +6662,29 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>367</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6654,7 +6699,7 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6663,17 +6708,19 @@
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>357</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="C44" s="2"/>
+      <c r="C44" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6682,7 +6729,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6691,10 +6738,10 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>364</v>
@@ -6702,11 +6749,9 @@
       <c r="M44" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6761,16 +6806,16 @@
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>369</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
@@ -6779,15 +6824,15 @@
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6798,7 +6843,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6810,16 +6855,20 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>103</v>
+        <v>376</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>104</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6867,19 +6916,19 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>106</v>
+        <v>375</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>382</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6888,7 +6937,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6896,21 +6945,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6922,17 +6971,15 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6981,19 +7028,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -7010,14 +7057,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7030,26 +7077,24 @@
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O47" t="s" s="2">
-        <v>196</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7097,7 +7142,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>117</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7118,7 +7163,7 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7126,42 +7171,46 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7185,13 +7234,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>380</v>
+        <v>77</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7209,19 +7258,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7230,7 +7279,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7238,10 +7287,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7261,16 +7310,16 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>103</v>
+        <v>228</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>104</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>105</v>
+        <v>392</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7297,13 +7346,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7321,7 +7370,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>106</v>
+        <v>390</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7330,10 +7379,10 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7342,7 +7391,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7350,10 +7399,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7361,11 +7410,11 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G50" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7376,13 +7425,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>277</v>
+        <v>104</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>278</v>
+        <v>105</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7421,31 +7470,31 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7454,7 +7503,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7462,14 +7511,12 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7478,7 +7525,7 @@
         <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7490,13 +7537,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>386</v>
+        <v>110</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>387</v>
+        <v>290</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>388</v>
+        <v>291</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7535,16 +7582,16 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>117</v>
@@ -7568,7 +7615,7 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7576,21 +7623,23 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7599,23 +7648,19 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>144</v>
+        <v>399</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>324</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7663,7 +7708,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>328</v>
+        <v>117</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7675,16 +7720,16 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>330</v>
+        <v>402</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7692,10 +7737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7706,7 +7751,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7718,19 +7763,19 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7779,13 +7824,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -7797,10 +7842,10 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7808,10 +7853,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7834,18 +7879,20 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7869,10 +7916,10 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>397</v>
+        <v>77</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>77</v>
@@ -7881,17 +7928,19 @@
         <v>77</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AC54" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7900,7 +7949,7 @@
         <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
@@ -7909,10 +7958,10 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7920,14 +7969,12 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>77</v>
       </c>
@@ -7948,16 +7995,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>103</v>
+        <v>406</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7986,7 +8033,7 @@
         <v>156</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>77</v>
@@ -7995,19 +8042,17 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8016,13 +8061,13 @@
         <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -8036,12 +8081,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8062,18 +8109,18 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>402</v>
+        <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8097,10 +8144,10 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>410</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>77</v>
@@ -8109,17 +8156,19 @@
         <v>77</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AC56" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8128,13 +8177,13 @@
         <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>77</v>
@@ -8143,19 +8192,17 @@
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>406</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8176,17 +8223,17 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8223,19 +8270,17 @@
         <v>77</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8250,7 +8295,7 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -8259,17 +8304,19 @@
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8290,18 +8337,18 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8349,7 +8396,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8364,7 +8411,7 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>77</v>
+        <v>422</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
@@ -8373,15 +8420,15 @@
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8401,19 +8448,19 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>373</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8463,7 +8510,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8487,15 +8534,15 @@
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>77</v>
+        <v>427</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8515,19 +8562,19 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>420</v>
+        <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8577,7 +8624,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8601,15 +8648,15 @@
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>424</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8620,7 +8667,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8629,21 +8676,21 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8691,13 +8738,13 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8712,18 +8759,18 @@
         <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>430</v>
+        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8746,19 +8793,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8807,7 +8852,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8825,21 +8870,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>438</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>77</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8862,19 +8907,19 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>220</v>
+        <v>446</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8899,31 +8944,31 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8941,10 +8986,10 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>77</v>
+        <v>451</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>77</v>
+        <v>452</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8952,10 +8997,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8978,19 +9023,19 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>447</v>
+        <v>228</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9015,13 +9060,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>77</v>
+        <v>458</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9039,7 +9084,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9063,6 +9108,122 @@
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:22:25+00:00</t>
+    <t>2026-06-11T14:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-goal-projet-vie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:21:35+00:00</t>
+    <t>2026-06-11T15:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -669,6 +669,10 @@
   </si>
   <si>
     <t>External Ids for this goal</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+GoalProjetVieIdentifierFormat:l'identifiant du projet de vie doit respecter le format :  3+FINESS/identifiantLocalUsagerESSMS-PDV-idLocalProjetVie {value.matches('^3[0-9]{9}/[A-Za-z0-9]+-PDV-[A-Za-z0-9]+$')}</t>
   </si>
   <si>
     <t>Goal.identifier:idPDV.id</t>
@@ -4076,7 +4080,7 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -4093,10 +4097,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4205,10 +4209,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4319,10 +4323,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4348,16 +4352,16 @@
         <v>166</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4382,13 +4386,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4406,7 +4410,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4427,7 +4431,7 @@
         <v>189</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4435,10 +4439,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4461,19 +4465,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4483,7 +4487,7 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>77</v>
@@ -4501,10 +4505,10 @@
         <v>148</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4522,7 +4526,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4540,10 +4544,10 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4551,10 +4555,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4580,16 +4584,16 @@
         <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4599,10 +4603,10 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4638,7 +4642,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4656,10 +4660,10 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4667,10 +4671,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4696,13 +4700,13 @@
         <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4716,7 +4720,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4752,7 +4756,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4770,10 +4774,10 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4781,10 +4785,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4807,13 +4811,13 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4864,7 +4868,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4882,10 +4886,10 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4893,10 +4897,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4919,16 +4923,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4978,7 +4982,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4996,10 +5000,10 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5007,10 +5011,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5036,16 +5040,16 @@
         <v>166</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5070,13 +5074,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5094,7 +5098,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>89</v>
@@ -5109,24 +5113,24 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5152,10 +5156,10 @@
         <v>103</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5235,10 +5239,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5264,10 +5268,10 @@
         <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5345,13 +5349,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>77</v>
@@ -5373,13 +5377,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5439,13 +5443,13 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
@@ -5459,10 +5463,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5488,10 +5492,10 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5542,7 +5546,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5571,10 +5575,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5597,13 +5601,13 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5633,10 +5637,10 @@
         <v>170</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5654,7 +5658,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5675,7 +5679,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5683,10 +5687,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5709,17 +5713,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5747,10 +5751,10 @@
         <v>156</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5768,7 +5772,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5792,15 +5796,15 @@
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5823,19 +5827,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5863,10 +5867,10 @@
         <v>170</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5884,7 +5888,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5905,18 +5909,18 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5939,19 +5943,19 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5979,10 +5983,10 @@
         <v>156</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6000,7 +6004,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -6018,21 +6022,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6141,10 +6145,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6255,10 +6259,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6284,16 +6288,16 @@
         <v>144</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6342,7 +6346,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6360,10 +6364,10 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6371,10 +6375,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6400,16 +6404,16 @@
         <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6458,7 +6462,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6473,13 +6477,13 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6487,10 +6491,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6513,17 +6517,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6572,7 +6576,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>89</v>
@@ -6587,24 +6591,24 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6627,17 +6631,17 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6665,16 +6669,16 @@
         <v>156</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -6684,7 +6688,7 @@
         <v>116</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6708,18 +6712,18 @@
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>77</v>
@@ -6741,17 +6745,17 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6800,7 +6804,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6815,7 +6819,7 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
@@ -6824,15 +6828,15 @@
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6855,19 +6859,19 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6916,7 +6920,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6925,10 +6929,10 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6945,10 +6949,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7057,10 +7061,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7171,14 +7175,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7200,10 +7204,10 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>113</v>
@@ -7258,7 +7262,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7287,10 +7291,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7313,13 +7317,13 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7349,10 +7353,10 @@
         <v>156</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7370,7 +7374,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7379,7 +7383,7 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>101</v>
@@ -7399,10 +7403,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7511,10 +7515,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7540,10 +7544,10 @@
         <v>110</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7623,13 +7627,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="B52" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="C52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -7651,13 +7655,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7729,7 +7733,7 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7737,10 +7741,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7766,16 +7770,16 @@
         <v>144</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7824,7 +7828,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7842,10 +7846,10 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7853,10 +7857,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7882,16 +7886,16 @@
         <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7940,7 +7944,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7958,10 +7962,10 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7969,10 +7973,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7995,16 +7999,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8033,7 +8037,7 @@
         <v>156</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>77</v>
@@ -8042,7 +8046,7 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -8052,7 +8056,7 @@
         <v>116</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8061,7 +8065,7 @@
         <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8081,13 +8085,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8112,13 +8116,13 @@
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8147,7 +8151,7 @@
         <v>156</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>77</v>
@@ -8168,7 +8172,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8177,13 +8181,13 @@
         <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>77</v>
@@ -8197,10 +8201,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8223,17 +8227,17 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8270,7 +8274,7 @@
         <v>77</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
@@ -8280,7 +8284,7 @@
         <v>116</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8304,18 +8308,18 @@
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>77</v>
@@ -8337,17 +8341,17 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8396,7 +8400,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8411,7 +8415,7 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
@@ -8420,15 +8424,15 @@
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8451,16 +8455,16 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8510,7 +8514,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8534,15 +8538,15 @@
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8568,13 +8572,13 @@
         <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8624,7 +8628,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8653,10 +8657,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8679,16 +8683,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8738,7 +8742,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8762,15 +8766,15 @@
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8793,17 +8797,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8852,7 +8856,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8873,18 +8877,18 @@
         <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8907,19 +8911,19 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8968,7 +8972,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8986,10 +8990,10 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8997,10 +9001,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9023,19 +9027,19 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9063,10 +9067,10 @@
         <v>156</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9084,7 +9088,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9113,10 +9117,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9139,19 +9143,19 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9200,7 +9204,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
